--- a/docs/api-documentation.xlsx
+++ b/docs/api-documentation.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="125">
   <si>
     <t>כתובת</t>
   </si>
@@ -52,7 +52,7 @@
     <t>רישום לקוח חדש</t>
   </si>
   <si>
-    <t>post</t>
+    <t>POST</t>
   </si>
   <si>
     <t>ציבורי (ללא הרשאה)</t>
@@ -91,16 +91,37 @@
     <t>404 - לקוח לא נמצא | 401 - סיסמה שגויה</t>
   </si>
   <si>
+    <t>/api/auth/change-password</t>
+  </si>
+  <si>
+    <t>שינוי סיסמה למשתמש המחובר</t>
+  </si>
+  <si>
+    <t>משתמש מחובר</t>
+  </si>
+  <si>
+    <t>currentPassword: string, newPassword: string (מינ' 6 תווים, שונה מהנוכחית)</t>
+  </si>
+  <si>
+    <t>{ message }</t>
+  </si>
+  <si>
+    <t>Update</t>
+  </si>
+  <si>
+    <t>401 - הסיסמה הנוכחית שגויה | 400 - סיסמה חדשה לא תקינה</t>
+  </si>
+  <si>
+    <t>Authorization</t>
+  </si>
+  <si>
     <t>/api/auth/me</t>
   </si>
   <si>
     <t>מחזיר את פרטי הלקוח המחובר לפי הטוקן</t>
   </si>
   <si>
-    <t>get</t>
-  </si>
-  <si>
-    <t>משתמש מחובר</t>
+    <t>GET</t>
   </si>
   <si>
     <t>{ _id, firstName, lastName, email, address, role }</t>
@@ -109,9 +130,6 @@
     <t>401 - טוקן חסר/לא תקין</t>
   </si>
   <si>
-    <t>Authorization</t>
-  </si>
-  <si>
     <t>/api/category</t>
   </si>
   <si>
@@ -145,7 +163,7 @@
     <t>name: string, slug: string, description: string</t>
   </si>
   <si>
-    <t>body: eyebrow, intro, bannerAlt, productsTitle - string</t>
+    <t>body: eyebrow, intro, bannerAlt, productsTitle, icon, soldByWeight, image - file</t>
   </si>
   <si>
     <t>409 - slug כפול | 400 - שדה חסר/לא תקין | 401/403</t>
@@ -154,25 +172,19 @@
     <t>מעדכן קטגוריה קיימת</t>
   </si>
   <si>
-    <t>put</t>
-  </si>
-  <si>
-    <t>body: name, slug, description, eyebrow, intro, bannerAlt, productsTitle - string</t>
-  </si>
-  <si>
-    <t>Update</t>
+    <t>PUT</t>
+  </si>
+  <si>
+    <t>body: name, slug, description, eyebrow, intro, bannerAlt, productsTitle, icon, soldByWeight, image</t>
   </si>
   <si>
     <t>404 - לא נמצאה | 409 - slug כפול | 400 | 401/403</t>
   </si>
   <si>
-    <t>מוחק קטגוריה לפי מזהה</t>
-  </si>
-  <si>
-    <t>delete</t>
-  </si>
-  <si>
-    <t>{ message }</t>
+    <t>מוחק קטגוריה לפי מזהה (מוחק גם את המוצרים שלה)</t>
+  </si>
+  <si>
+    <t>DELETE</t>
   </si>
   <si>
     <t>Delete</t>
@@ -265,7 +277,10 @@
     <t>מעדכן פרטי לקוח</t>
   </si>
   <si>
-    <t>body: firstName, lastName, email, address, password, paymentMethod</t>
+    <t>משתמש מחובר (הבעלים)</t>
+  </si>
+  <si>
+    <t>body: firstName, lastName, email, address, paymentMethod</t>
   </si>
   <si>
     <t>403 - אין הרשאה | 404 - לא נמצא | 400</t>
@@ -310,16 +325,16 @@
     <t>403 - אין הרשאה | 404 - לא נמצאה</t>
   </si>
   <si>
-    <t>יוצר הזמנה חדשה, מעדכן מלאי ומחשב מחיר כולל</t>
-  </si>
-  <si>
-    <t>customerId: string, items: [{productId, qty}] (מינימום פריט אחד)</t>
+    <t>יוצר הזמנה חדשה, מעדכן מלאי, מחשב מחיר כולל ושולח מייל אישור ללקוח</t>
+  </si>
+  <si>
+    <t>items: [{productId, qty}] (מינימום פריט אחד), phone: string</t>
   </si>
   <si>
     <t>{ _id, customerId, items, totalPrice, deliveryFee, status, orderDate }</t>
   </si>
   <si>
-    <t>403 - customerId לא תואם למשתמש המחובר | 404 - מוצר/לקוח לא נמצא | 409 - אין מספיק מלאי | 400</t>
+    <t>404 - מוצר/לקוח לא נמצא | 409 - אין מספיק מלאי | 400 | 503 - חסום בשעות שבת</t>
   </si>
   <si>
     <t>/api/order/{id}/status</t>
@@ -350,13 +365,34 @@
   </si>
   <si>
     <t>body: attachment - file</t>
+  </si>
+  <si>
+    <t>מחזיר את כל הפניות שהתקבלו (החדשות קודם)</t>
+  </si>
+  <si>
+    <t>message[] - [{ _id, name, email, subject, message, attachment, handled }]</t>
+  </si>
+  <si>
+    <t>/api/message/{id}/status</t>
+  </si>
+  <si>
+    <t>מסמן פנייה כטופלה/לא טופלה (מוחק את הקובץ המצורף בטיפול ראשון)</t>
+  </si>
+  <si>
+    <t>handled: boolean</t>
+  </si>
+  <si>
+    <t>קוד הודעה - {id}</t>
+  </si>
+  <si>
+    <t>{ _id, handled, ... }</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -369,8 +405,15 @@
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -379,12 +422,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2F5597"/>
+        <fgColor rgb="FF1D6B57"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F6FB"/>
+        <fgColor rgb="FFF7F9F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F2E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3ECFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE3E3"/>
       </patternFill>
     </fill>
   </fills>
@@ -397,24 +460,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF18322F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color rgb="FFE0E0E0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -422,16 +481,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -772,22 +843,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="46" customWidth="1"/>
-    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="7" max="8" width="42" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="40" customWidth="1"/>
+    <col min="10" max="10" width="42" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -822,14 +892,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -857,56 +927,56 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="F3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="H3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K3" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>16</v>
@@ -918,59 +988,59 @@
         <v>16</v>
       </c>
       <c r="I4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>14</v>
@@ -979,10 +1049,10 @@
         <v>16</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>16</v>
@@ -991,348 +1061,348 @@
         <v>24</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="3" t="s">
+    <row r="7" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" s="3" t="s">
+      <c r="B9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="3" t="s">
+      <c r="G9" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="H9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="D11" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="I10" s="2" t="s">
+      <c r="E11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="I11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" s="3" t="s">
+      <c r="J11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>13</v>
+      <c r="C12" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="G12" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>68</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>69</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="H13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I13" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="J13" s="3" t="s">
+      <c r="F13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>52</v>
+        <v>73</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J15" s="3" t="s">
+      <c r="C15" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J15" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K15" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>78</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>28</v>
+      <c r="C16" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>16</v>
@@ -1341,129 +1411,129 @@
         <v>24</v>
       </c>
       <c r="J16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="K16" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="C17" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19" s="3" t="s">
+      <c r="H19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J19" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="K19" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K19" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>28</v>
+        <v>93</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>16</v>
@@ -1472,7 +1542,7 @@
         <v>16</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>16</v>
@@ -1481,188 +1551,294 @@
         <v>24</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B21" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="B21" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="E21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="H21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="J21" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K21" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="B25" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22" s="2" t="s">
+      <c r="D26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J22" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G24" s="2" t="s">
+      <c r="J26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C28" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="H24" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>16</v>
+      <c r="D28" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/api-documentation.xlsx
+++ b/docs/api-documentation.xlsx
@@ -1,10 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_5D393C81444A46D776CC62C7270BDC2B0F02B323" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="API Documentation" state="visible" r:id="rId4"/>
+    <sheet name="API Documentation" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -391,26 +395,29 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="8">
@@ -842,9 +849,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K28"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -857,7 +864,7 @@
     <col min="11" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -892,7 +899,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -927,7 +934,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
@@ -962,7 +969,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>26</v>
       </c>
@@ -997,7 +1004,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>34</v>
       </c>
@@ -1032,7 +1039,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>39</v>
       </c>
@@ -1067,7 +1074,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>42</v>
       </c>
@@ -1102,7 +1109,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>39</v>
       </c>
@@ -1137,7 +1144,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>42</v>
       </c>
@@ -1172,7 +1179,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>42</v>
       </c>
@@ -1207,7 +1214,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>60</v>
       </c>
@@ -1242,7 +1249,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>64</v>
       </c>
@@ -1277,7 +1284,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>60</v>
       </c>
@@ -1312,7 +1319,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>64</v>
       </c>
@@ -1347,7 +1354,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>64</v>
       </c>
@@ -1382,7 +1389,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>78</v>
       </c>
@@ -1417,7 +1424,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>82</v>
       </c>
@@ -1452,7 +1459,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>82</v>
       </c>
@@ -1487,7 +1494,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>82</v>
       </c>
@@ -1522,7 +1529,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>92</v>
       </c>
@@ -1557,7 +1564,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>95</v>
       </c>
@@ -1592,7 +1599,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>99</v>
       </c>
@@ -1627,7 +1634,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>92</v>
       </c>
@@ -1662,7 +1669,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>108</v>
       </c>
@@ -1697,7 +1704,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>99</v>
       </c>
@@ -1732,7 +1739,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>113</v>
       </c>
@@ -1767,7 +1774,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>113</v>
       </c>
@@ -1802,7 +1809,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>120</v>
       </c>
@@ -1838,8 +1845,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:K1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>